--- a/docs/宮城県_変電所リスト_社内用.xlsx
+++ b/docs/宮城県_変電所リスト_社内用.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>社外提示=◎○のみ（別ファイル）。△=空容量小さめ/条件悪。都心=空容量はあるが用地確保困難。スコア・座標・実績は社外に出さないこと。</t>
+          <t>社外提示=◎○のみ（別ファイル）。△=空容量小さめ/条件悪。都心=空容量はあるが用地確保困難。スコア・実績は社外に出さないこと（座標は社外用にも掲載）。</t>
         </is>
       </c>
     </row>

--- a/docs/宮城県_変電所リスト_社内用.xlsx
+++ b/docs/宮城県_変電所リスト_社内用.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>社外提示=◎○のみ（別ファイル）。△=空容量小さめ/条件悪。都心=空容量はあるが用地確保困難。スコア・実績は社外に出さないこと（座標は社外用にも掲載）。</t>
+          <t>社外提示=◎のみ（別ファイル）。○=条件付き候補（社内のみ）。△=空容量小さめ/条件悪。都心=空容量はあるが用地確保困難。スコア・実績は社外に出さないこと（座標は社外用にも掲載）。</t>
         </is>
       </c>
     </row>
